--- a/docs/package/05_Delivery/BrokerVerse_Implementation_Plan.xlsx
+++ b/docs/package/05_Delivery/BrokerVerse_Implementation_Plan.xlsx
@@ -3030,7 +3030,7 @@
       </c>
       <c r="F23" s="17" t="inlineStr">
         <is>
-          <t>Branding decisions; client marks permission needed or not</t>
+          <t>Branding decisions; client brand pack needed or not, with its contract reference</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
@@ -4383,7 +4383,7 @@
       <c r="X41" s="22" t="n"/>
       <c r="Y41" s="21" t="n"/>
     </row>
-    <row r="42" ht="30" customHeight="1">
+    <row r="42" ht="40" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
           <t>R8</t>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>Written permission to use client marks (only with a client brand pack)</t>
+          <t>Contract reference covering the use of the client's marks on the engagement file (client brand pack only)</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>Permission letter on the engagement file</t>
+          <t>Contract reference on the engagement file</t>
         </is>
       </c>
       <c r="G42" s="17" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>Client brand pack applied (only with written permission, for example the Toyota Insurance Services pack)</t>
+          <t>Client brand pack applied only in that client's environments under its contract with iorta TechNXT (for example the Toyota Insurance Services pack)</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>Pack applied; permission on file</t>
+          <t>Pack enabled with the engagement confirmation; contract reference on file</t>
         </is>
       </c>
       <c r="G57" s="17" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="F21" s="17" t="inlineStr">
         <is>
-          <t>Branding decisions; client marks permission needed or not</t>
+          <t>Branding decisions; client brand pack needed or not, with its contract reference</t>
         </is>
       </c>
       <c r="G21" s="17" t="inlineStr">
@@ -10940,7 +10940,7 @@
       <c r="AB41" s="21" t="n"/>
       <c r="AC41" s="21" t="n"/>
     </row>
-    <row r="42" ht="30" customHeight="1">
+    <row r="42" ht="40" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
           <t>R8</t>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>Written permission to use client marks (only with a client brand pack)</t>
+          <t>Contract reference covering the use of the client's marks on the engagement file (client brand pack only)</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="F42" s="17" t="inlineStr">
         <is>
-          <t>Permission letter on the engagement file</t>
+          <t>Contract reference on the engagement file</t>
         </is>
       </c>
       <c r="G42" s="17" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>Client brand pack applied (only with written permission, for example the Toyota Insurance Services pack)</t>
+          <t>Client brand pack applied only in that client's environments under its contract with iorta TechNXT (for example the Toyota Insurance Services pack)</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
@@ -12063,7 +12063,7 @@
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>Pack applied; permission on file</t>
+          <t>Pack enabled with the engagement confirmation; contract reference on file</t>
         </is>
       </c>
       <c r="G57" s="17" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>Branding decisions; client marks permission needed or not</t>
+          <t>Branding decisions; client brand pack needed or not, with its contract reference</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
@@ -18146,7 +18146,7 @@
       <c r="AJ42" s="21" t="n"/>
       <c r="AK42" s="21" t="n"/>
     </row>
-    <row r="43" ht="30" customHeight="1">
+    <row r="43" ht="40" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
           <t>R8</t>
@@ -18159,7 +18159,7 @@
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>Written permission to use client marks (only with a client brand pack)</t>
+          <t>Contract reference covering the use of the client's marks on the engagement file (client brand pack only)</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
@@ -18174,7 +18174,7 @@
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>Permission letter on the engagement file</t>
+          <t>Contract reference on the engagement file</t>
         </is>
       </c>
       <c r="G43" s="17" t="inlineStr">
@@ -19281,7 +19281,7 @@
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>Client brand pack applied (only with written permission, for example the Toyota Insurance Services pack)</t>
+          <t>Client brand pack applied only in that client's environments under its contract with iorta TechNXT (for example the Toyota Insurance Services pack)</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>Pack applied; permission on file</t>
+          <t>Pack enabled with the engagement confirmation; contract reference on file</t>
         </is>
       </c>
       <c r="G57" s="17" t="inlineStr">
@@ -24133,7 +24133,7 @@
       </c>
       <c r="F22" s="17" t="inlineStr">
         <is>
-          <t>Branding decisions; client marks permission needed or not</t>
+          <t>Branding decisions; client brand pack needed or not, with its contract reference</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
@@ -26014,7 +26014,7 @@
       <c r="AP42" s="21" t="n"/>
       <c r="AQ42" s="21" t="n"/>
     </row>
-    <row r="43" ht="30" customHeight="1">
+    <row r="43" ht="40" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
           <t>R8</t>
@@ -26027,7 +26027,7 @@
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>Written permission to use client marks (only with a client brand pack)</t>
+          <t>Contract reference covering the use of the client's marks on the engagement file (client brand pack only)</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="F43" s="17" t="inlineStr">
         <is>
-          <t>Permission letter on the engagement file</t>
+          <t>Contract reference on the engagement file</t>
         </is>
       </c>
       <c r="G43" s="17" t="inlineStr">
@@ -27233,7 +27233,7 @@
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>Client brand pack applied (only with written permission, for example the Toyota Insurance Services pack)</t>
+          <t>Client brand pack applied only in that client's environments under its contract with iorta TechNXT (for example the Toyota Insurance Services pack)</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
@@ -27248,7 +27248,7 @@
       </c>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>Pack applied; permission on file</t>
+          <t>Pack enabled with the engagement confirmation; contract reference on file</t>
         </is>
       </c>
       <c r="G57" s="17" t="inlineStr">
@@ -32666,7 +32666,7 @@
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Written permission to use client marks (only with a client brand pack)</t>
+          <t>Contract reference covering the use of the client's marks on the engagement file (client brand pack only)</t>
         </is>
       </c>
       <c r="E45" s="10" t="inlineStr">
@@ -33480,7 +33480,7 @@
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>Client brand pack applied (only with written permission, for example the Toyota Insurance Services pack)</t>
+          <t>Client brand pack applied only in that client's environments under its contract with iorta TechNXT (for example the Toyota Insurance Services pack)</t>
         </is>
       </c>
       <c r="E67" s="10" t="inlineStr">
@@ -33507,7 +33507,7 @@
       </c>
       <c r="B68" s="10" t="inlineStr">
         <is>
-          <t>Written permission to use client marks (only with a client brand pack)</t>
+          <t>Contract reference covering the use of the client's marks on the engagement file (client brand pack only)</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
@@ -33517,7 +33517,7 @@
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Client brand pack applied (only with written permission, for example the Toyota Insurance Services pack)</t>
+          <t>Client brand pack applied only in that client's environments under its contract with iorta TechNXT (for example the Toyota Insurance Services pack)</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
@@ -37541,7 +37541,7 @@
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>Permission to use client marks (client brand pack)</t>
+          <t>Contract reference covering the use of client marks (client brand pack)</t>
         </is>
       </c>
       <c r="C26" s="33" t="inlineStr">
